--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>55</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>30/07 23:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>50</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>03/08 18:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>03/08 23:20</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>45</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>29/07 21:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>45</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>60</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>29/07 18:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>50</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>08/08 00:15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F19" t="n">
+        <v>4.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>02/08 16:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>35</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.75</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>29/07 17:40</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F22" t="n">
+        <v>2.6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>02/08 15:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F23" t="n">
+        <v>1.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>45</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>55</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>40</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,97 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45867.09012404073</v>
+        <v>45867.09012403935</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Lorenzo Mu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti – James DuckworthATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>29/07 17:40</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+8,35%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45867.17297913416</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 21-2- se qualifie | FC Iberia </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999 – Levadia TallinnEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>29/07 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>48,2%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+1,11%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45867.17297913416</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>29/07 17:40</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>4.90</t>
-        </is>
+      <c r="F27" t="n">
+        <v>4.9</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45867.17297913416</v>
+        <v>45867.17297913194</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>29/07 16:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45867.17297913416</v>
+        <v>45867.17297913194</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Panathinai</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Panathinaikos – Glasgow RangersEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>30/07 18:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+38,9%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45867.23007479288</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,142 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45867.23007479288</v>
+        <v>45867.23007479167</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 2 - aces | Alexandre </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Alexandre Muller – Miomir KecmanovicATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>29/07 16:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+9,53%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45867.27544622052</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Emilio Nav</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Emilio Nava – Ugo HumbertATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+7,45%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45867.27544622052</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Karen Khac</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Karen Khachanov – Juan Pablo FicovichATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>29/07 16:10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>81,9%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+6,50%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45867.27544622052</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>29/07 16:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.65</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45867.27544622052</v>
+        <v>45867.27544621528</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>4.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45867.27544622052</v>
+        <v>45867.27544621528</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>29/07 16:10</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F32" t="n">
+        <v>1.3</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,142 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45867.27544622052</v>
+        <v>45867.27544621528</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | T.Griekspo</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>T.Griekspoor – T.EtcheverryATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>29/07 17:40</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+27,8%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45867.31046308306</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 5.5 - tirs2e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Lincoln Red Imps FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 5.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>33,7%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+18,1%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45867.31046308306</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tirs2e équipe | Dynamo Kie</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dynamo Kiev – Hamrun SpartansEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>29/07 18:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>34,8%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+2,04%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45867.31046308306</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>29/07 17:40</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45867.31046308306</v>
+        <v>45867.31046307871</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45867.31046308306</v>
+        <v>45867.31046307871</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>29/07 18:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.93</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,367 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45867.31046308306</v>
+        <v>45867.31046307871</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Nicolas Ar</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nicolas Arseneault – Alexei PopyrinATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>29/07 17:20</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+156%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | A.Ito – J.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A.Ito – J.PaoliniWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>29/07 18:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+61,9%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Zverev –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A.Zverev – A.WaltonATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>30/07 00:10</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+48,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Nuno Borge</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nuno Borges – Facundo BagnisATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29/07 18:50</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>71,3%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+42,7%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | C.Moutet –</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C.Moutet – J.BrooksbyATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>29/07 17:40</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>49,9%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+24,7%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | R.Safiulli</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>R.Safiullin – C.RuudATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>29/07 21:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>76,1%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+21,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | K.Khachano</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>K.Khachanov – JP.FicovichATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>29/07 16:10</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>23,6%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+17,9%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45867.35612642405</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | E.Nava – U</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>E.Nava – U.Humbert385076e7 ATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>80,3%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+8,46%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45867.35612642405</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>29/07 17:20</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>8</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>29/07 18:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>30/07 00:10</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="39">
@@ -2102,10 +2096,8 @@
           <t>29/07 18:50</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2118,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="40">
@@ -2147,10 +2139,8 @@
           <t>29/07 17:40</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2163,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="41">
@@ -2192,10 +2182,8 @@
           <t>29/07 21:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F41" t="n">
+        <v>1.6</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2208,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="42">
@@ -2237,10 +2225,8 @@
           <t>29/07 16:10</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2253,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
       </c>
     </row>
     <row r="43">
@@ -2282,10 +2268,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
+      <c r="F43" t="n">
+        <v>1.35</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2298,7 +2282,232 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45867.35612642405</v>
+        <v>45867.35612642361</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | 2 - aces | Alexander </t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Alexander Zverev – Adam WaltonATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>30/07 00:10</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+69,8%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45867.39566020058</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Kairat Alm</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Kairat Almaty – KuPS KuopioLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+21,6%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45867.39566020058</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Roman Safi</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Roman Safiullin – Casper RuudATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>29/07 21:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>75,3%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45867.39566020058</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tirs2e équipe | Zrinjski M</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Zrinjski Mostar – Slovan BratislavaEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+8,70%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45867.39566020058</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tirs2e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Lincoln Red Imps FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>45,0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+5,84%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45867.39566020058</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>30/07 00:10</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45867.39566020058</v>
+        <v>45867.39566019676</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45867.39566020058</v>
+        <v>45867.39566019676</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>29/07 21:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.6</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45867.39566020058</v>
+        <v>45867.39566019676</v>
       </c>
     </row>
     <row r="47">
@@ -2446,10 +2440,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F47" t="n">
+        <v>3.2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2462,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45867.39566020058</v>
+        <v>45867.39566019676</v>
       </c>
     </row>
     <row r="48">
@@ -2491,10 +2483,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.35</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2507,7 +2497,187 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45867.39566020058</v>
+        <v>45867.39566019676</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Sportivo T</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>02/08 19:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+41,7%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45867.43483765514</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | N.Borges –</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>N.Borges – F.BagnisATP - Toronto A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>29/07 18:50</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+20,1%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45867.43483765514</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs2e équipe | KF Drita –</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>KF Drita – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>29/07 18:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+6,04%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45867.43483765514</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Jaume Muna</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jaume Munar – Francisco CerundoloATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>29/07 18:50</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>65,9%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+5,37%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45867.43483765514</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>02/08 19:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>55</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45867.43483765514</v>
+        <v>45867.43483765046</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>29/07 18:50</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F50" t="n">
+        <v>2.5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45867.43483765514</v>
+        <v>45867.43483765046</v>
       </c>
     </row>
     <row r="51">
@@ -2616,10 +2612,8 @@
           <t>29/07 18:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.4</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2632,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45867.43483765514</v>
+        <v>45867.43483765046</v>
       </c>
     </row>
     <row r="52">
@@ -2661,10 +2655,8 @@
           <t>29/07 18:50</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F52" t="n">
+        <v>1.6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2677,7 +2669,142 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45867.43483765514</v>
+        <v>45867.43483765046</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Panathinai</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Panathinaikos – Glasgow RangersEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/07 18:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45867.47277608456</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 4.51er set2e participant | Aoi Ito – </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Aoi Ito – Jasmine PaoliniWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>29/07 18:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45867.47277608456</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 2.5 - aces1er participant | Corentin M</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Corentin Moutet – Jenson BrooksbyATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 2.5 - aces1er participant</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29/07 17:40</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+7,50%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45867.47277608456</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>30/07 18:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F53" t="n">
+        <v>2.6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45867.47277608456</v>
+        <v>45867.47277608796</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>29/07 18:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>6.70</t>
-        </is>
+      <c r="F54" t="n">
+        <v>6.7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45867.47277608456</v>
+        <v>45867.47277608796</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>29/07 17:40</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.15</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,187 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45867.47277608456</v>
+        <v>45867.47277608796</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Fomget Gen</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fomget Genclick Ve Spor F. – Baku F.Europe - Ligue des Champions F.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>30/07 16:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+33,7%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45867.53590342817</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Los Angele</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Los Angeles FC – Mazatlan FCLeagues Cup</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>30/07 02:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45867.53590342817</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 2.5 - break | Reilly Ope</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Reilly Opelka – Tomas MachacATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 2.5 - break</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>29/07 20:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>56,3%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45867.53590342817</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Moins que 30.51re période | Cameroun (</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cameroun (F) – Angola (F)International - Championnat d'Afrique (F)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Moins que 30.51re période</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>48,6%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45867.53590342817</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>30/07 16:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>125</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45867.53590342817</v>
+        <v>45867.53590342592</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>30/07 02:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45867.53590342817</v>
+        <v>45867.53590342592</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>29/07 20:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45867.53590342817</v>
+        <v>45867.53590342592</v>
       </c>
     </row>
     <row r="59">
@@ -2962,10 +2956,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.3</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2978,7 +2970,52 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45867.53590342817</v>
+        <v>45867.53590342592</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Flora Tall</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Flora Tallinn – Sfk RigaLigue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>30/07 11:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+52,9%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45867.57138440995</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>30/07 11:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,277 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45867.57138440995</v>
+        <v>45867.57138440972</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | Tukums 200</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tukums 2000 – FC RigaLettonie. Lettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>03/08 15:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+65,2%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45867.60246469326</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Zilina – T</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Zilina – Tatran PresovFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>03/08 17:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+29,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45867.60246469326</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | SC Grobina</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SC Grobinas – Rigas Futbola SkolaLettonie. Lettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>03/08 15:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+28,1%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45867.60246469326</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Lincoln Red Imps FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>29/07 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,90%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+14,1%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45867.60246469326</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Kairat Alm</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kairat Almaty – Kuopio PSEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>29/07 15:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+9,61%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45867.60246469326</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 4.51er set2e participant | Daniil Med</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev – Dalibor SvrcinaATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>29/07 22:10</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+8,29%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45867.60246469326</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>03/08 15:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>15</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45867.60246469326</v>
+        <v>45867.6024646875</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>45</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45867.60246469326</v>
+        <v>45867.6024646875</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>03/08 15:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>20</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45867.60246469326</v>
+        <v>45867.6024646875</v>
       </c>
     </row>
     <row r="64">
@@ -3177,10 +3171,8 @@
           <t>29/07 19:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>60</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3193,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45867.60246469326</v>
+        <v>45867.6024646875</v>
       </c>
     </row>
     <row r="65">
@@ -3222,10 +3214,8 @@
           <t>29/07 15:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
+      <c r="F65" t="n">
+        <v>2.17</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3238,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45867.60246469326</v>
+        <v>45867.6024646875</v>
       </c>
     </row>
     <row r="66">
@@ -3267,10 +3257,8 @@
           <t>29/07 22:10</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F66" t="n">
+        <v>3.4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3283,7 +3271,187 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45867.60246469326</v>
+        <v>45867.6024646875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Pas de buts | Fomget Gen</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fomget Genclick Ve Spor – Neftchi Baku PFCLigue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>30/07 16:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+38,5%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45867.64446530355</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | H 1 (+1)1re période | Cardiff Ci</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cardiff City (F) – Athlone Town FCEurope - Ligue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>H 1 (+1)1re période</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>30/07 18:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+12,6%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45867.64446530355</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 5.51er set2e participant | Coco Gauff</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Coco Gauff – Danielle CollinsWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>29/07 23:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45867.64446530355</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | 1 / DNB | Jelgava – </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Jelgava – FK LiepajaLettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1 / DNB</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02/08 12:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+8,78%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45867.64446530355</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,10 +3300,8 @@
           <t>30/07 16:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>125</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3316,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45867.64446530355</v>
+        <v>45867.64446530092</v>
       </c>
     </row>
     <row r="68">
@@ -3345,10 +3343,8 @@
           <t>30/07 18:30</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F68" t="n">
+        <v>2.75</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3361,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45867.64446530355</v>
+        <v>45867.64446530092</v>
       </c>
     </row>
     <row r="69">
@@ -3390,10 +3386,8 @@
           <t>29/07 23:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F69" t="n">
+        <v>2.85</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3406,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45867.64446530355</v>
+        <v>45867.64446530092</v>
       </c>
     </row>
     <row r="70">
@@ -3435,10 +3429,8 @@
           <t>02/08 12:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F70" t="n">
+        <v>2.55</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3451,7 +3443,277 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45867.64446530355</v>
+        <v>45867.64446530092</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | 1X | Cardiff Ci</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cardiff City fc – Athlone Town FCLigue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>30/07 18:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+16,9%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45867.68755248054</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | M.Bouzkova</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>M.Bouzkova – D.ShnaiderWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>29/07 18:50</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45867.68755248054</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 26 jeux | C.Gauff – </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>C.Gauff – D.CollinsWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>26 jeux</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>29/07 23:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45867.68755248054</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 3.5 - break1er participant | Nuno Borge</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Nuno Borges – Facundo BagnisATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break1er participant</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>29/07 18:50</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45867.68755248054</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 3.5 - aces2e participant | Denis Shap</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Denis Shapovalov – Learner TienATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - aces2e participant</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>29/07 23:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+7,88%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45867.68755248054</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Karen Khac</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Karen Khachanov – Juan Pablo FicovichATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>29/07 16:40</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+7,45%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45867.68755248054</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3472,10 +3472,8 @@
           <t>30/07 18:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
+      <c r="F71" t="n">
+        <v>9.050000000000001</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3488,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45867.68755248054</v>
+        <v>45867.68755247685</v>
       </c>
     </row>
     <row r="72">
@@ -3517,10 +3515,8 @@
           <t>29/07 18:50</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="F72" t="n">
+        <v>1.65</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3533,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45867.68755248054</v>
+        <v>45867.68755247685</v>
       </c>
     </row>
     <row r="73">
@@ -3562,10 +3558,8 @@
           <t>29/07 23:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="F73" t="n">
+        <v>5.5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45867.68755248054</v>
+        <v>45867.68755247685</v>
       </c>
     </row>
     <row r="74">
@@ -3607,10 +3601,8 @@
           <t>29/07 18:50</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F74" t="n">
+        <v>1.75</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3623,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45867.68755248054</v>
+        <v>45867.68755247685</v>
       </c>
     </row>
     <row r="75">
@@ -3652,10 +3644,8 @@
           <t>29/07 23:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F75" t="n">
+        <v>2.2</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3668,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45867.68755248054</v>
+        <v>45867.68755247685</v>
       </c>
     </row>
     <row r="76">
@@ -3697,10 +3687,8 @@
           <t>29/07 16:40</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>7</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3713,7 +3701,142 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45867.68755248054</v>
+        <v>45867.68755247685</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set2e participant | Adrian Man</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Adrian Mannarino – Ben SheltonATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>30/07 16:30</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45867.72552319735</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 21.5 - tirs | KF Drita –</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>KF Drita – CopenhagueEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Moins que 21.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>29/07 18:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+8,05%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45867.72552319735</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | Plus que 32.51re période | Cameroun (</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cameroun (F) – Angola (F)International - Championnat d'Afrique (F)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 32.51re période</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>30/07 21:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+6,78%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45867.72552319735</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -3730,10 +3730,8 @@
           <t>30/07 16:30</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45867.72552319735</v>
+        <v>45867.72552319444</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>29/07 18:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2.6</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45867.72552319735</v>
+        <v>45867.72552319444</v>
       </c>
     </row>
     <row r="79">
@@ -3820,10 +3816,8 @@
           <t>30/07 21:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F79" t="n">
+        <v>2.25</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3836,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45867.72552319735</v>
+        <v>45867.72552319444</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3833,6 +3833,51 @@
         <v>45867.72552319444</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | Cardiff Ci</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Cardiff City fc – Athlone Town FCLigue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>30/07 18:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+7,24%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45867.80740641124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,8 @@
           <t>30/07 18:30</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>40</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3875,7 +3873,97 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45867.80740641124</v>
+        <v>45867.80740641204</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Coco Gauff</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Coco Gauff – Danielle CollinsWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>29/07 23:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+14,1%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45867.85253916758</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | T.Schoolka</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>T.Schoolkate – M.Arnaldi385076e7 ATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>29/07 21:40</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+3,90%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45867.85253916758</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,10 +3902,8 @@
           <t>29/07 23:00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F81" t="n">
+        <v>4.2</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3918,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45867.85253916758</v>
+        <v>45867.85253916667</v>
       </c>
     </row>
     <row r="82">
@@ -3947,10 +3945,8 @@
           <t>29/07 21:40</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F82" t="n">
+        <v>1.5</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3963,7 +3959,187 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45867.85253916758</v>
+        <v>45867.85253916667</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Lokomotiva</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb – HNK Vukovar 1991HNL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>01/08 18:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+4,99%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45867.89138012019</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Bâle – </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FC Bâle – Grasshopper ZurichSuper League</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>02/08 18:30</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+1,93%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45867.89138012019</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | 2 | Racing FC </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Racing FC Union Luxembourg (F) – AEK AthensEurope - Ligue des Champions (F)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>30/07 17:00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+1,45%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45867.89138012019</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Chicago Sk</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago Sky – Washington MysticsUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>29/07 23:30</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+0,54%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45867.89138012019</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3988,10 +3988,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>45</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4004,7 +4002,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45867.89138012019</v>
+        <v>45867.89138011574</v>
       </c>
     </row>
     <row r="84">
@@ -4033,10 +4031,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>50</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45867.89138012019</v>
+        <v>45867.89138011574</v>
       </c>
     </row>
     <row r="85">
@@ -4078,10 +4074,8 @@
           <t>30/07 17:00</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
+      <c r="F85" t="n">
+        <v>1.58</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45867.89138012019</v>
+        <v>45867.89138011574</v>
       </c>
     </row>
     <row r="86">
@@ -4123,10 +4117,8 @@
           <t>29/07 23:30</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
+      <c r="F86" t="n">
+        <v>19</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4139,7 +4131,52 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45867.89138012019</v>
+        <v>45867.89138011574</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1(1:0) | FC Flora T</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FC Flora Talli – SFK RigaCoupes d'Europe - LDC (F)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1(1:0)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>30/07 11:00</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+1,46%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45867.93317444368</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-29.xlsx
+++ b/data/valuebets_database_2025-07-29.xlsx
@@ -4160,10 +4160,8 @@
           <t>30/07 11:00</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>5.10</t>
-        </is>
+      <c r="F87" t="n">
+        <v>5.1</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4176,7 +4174,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>45867.93317444368</v>
+        <v>45867.93317444444</v>
       </c>
     </row>
   </sheetData>
